--- a/artfynd/A 47346-2021 artfynd.xlsx
+++ b/artfynd/A 47346-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47346-2021 artfynd.xlsx
+++ b/artfynd/A 47346-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1738944</v>
+        <v>128596</v>
       </c>
       <c r="B2" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Apalbol, strax N om vägen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682851.672008961</v>
+        <v>682852</v>
       </c>
       <c r="R2" t="n">
-        <v>6638234.960095978</v>
+        <v>6638235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +752,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +786,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1379127</v>
+        <v>226438</v>
       </c>
       <c r="B3" t="n">
-        <v>90664</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Apalbol, Upl</t>
+          <t>Apalbol, strax S om vägen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682851.672008961</v>
+        <v>682885</v>
       </c>
       <c r="R3" t="n">
-        <v>6638234.960095978</v>
+        <v>6638368</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +863,14 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>funnen en vecka tidigare av Bengt Larsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +905,7 @@
         <v>1352762</v>
       </c>
       <c r="B4" t="n">
-        <v>85240</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682884.9497271791</v>
+        <v>682885</v>
       </c>
       <c r="R4" t="n">
-        <v>6638367.99128117</v>
+        <v>6638368</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,19 +970,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,53 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1551725</v>
+        <v>1379127</v>
       </c>
       <c r="B5" t="n">
-        <v>86135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4379</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalhamn, ca 1000 m N om, Upl</t>
+          <t>Apalbol, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>682884.9497271791</v>
+        <v>682852</v>
       </c>
       <c r="R5" t="n">
-        <v>6638367.99128117</v>
+        <v>6638235</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,21 +1072,11 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1088,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>skogsbilväg</t>
+          <t>örtrik 30-årig granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,62 +1106,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>226438</v>
+        <v>1551725</v>
       </c>
       <c r="B6" t="n">
-        <v>88895</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>720</v>
+        <v>4379</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Apalbol, strax S om vägen, Upl</t>
+          <t>Dalhamn, ca 1000 m N om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>682884.9497271791</v>
+        <v>682885</v>
       </c>
       <c r="R6" t="n">
-        <v>6638367.99128117</v>
+        <v>6638368</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,26 +1174,11 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>funnen en vecka tidigare av Bengt Larsson</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1256,7 +1190,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>örtrik 30-årig granskog</t>
+          <t>skogsbilväg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1274,46 +1208,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6220785</v>
+        <v>1278983</v>
       </c>
       <c r="B7" t="n">
-        <v>95520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224363</v>
+        <v>4404</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Hygrophorus camarophyllus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Apalbol, strax S om vägen, Upl</t>
+          <t>Apalbol, strax N om vägen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>682884.9497271791</v>
+        <v>682905</v>
       </c>
       <c r="R7" t="n">
-        <v>6638367.99128117</v>
+        <v>6638370</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1343,19 +1276,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,59 +1310,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128596</v>
+        <v>1738944</v>
       </c>
       <c r="B8" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Apalbol, strax N om vägen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>682851.672008961</v>
+        <v>682852</v>
       </c>
       <c r="R8" t="n">
-        <v>6638234.960095978</v>
+        <v>6638235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,19 +1378,9 @@
           <t>2008-09-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-09-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,6 +1409,104 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6220785</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Apalbol, strax S om vägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>682885</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6638368</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2008-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2008-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>örtrik 30-årig granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47346-2021 artfynd.xlsx
+++ b/artfynd/A 47346-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128596</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/226438</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1352762</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1379127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1551725</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1278983</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1738944</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,8 +1547,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6220785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>